--- a/human_resources_forms/032_employee_job_shadow_program_application_form--human_resources_forms.xlsx
+++ b/human_resources_forms/032_employee_job_shadow_program_application_form--human_resources_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -855,12 +855,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>job_shadow_program_details</t>
+          <t>job_shadow_program_details_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Job Shadow Program Details</t>
+          <t>Job Shadow Program Details 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -878,12 +878,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>submission_info</t>
+          <t>submission_info_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Submission Info</t>
+          <t>Submission Info 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -901,12 +901,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>submission_status</t>
+          <t>submission_status_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Submission Status</t>
+          <t>Submission Status 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -952,7 +952,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Submission Info 2</t>
+          <t>Submission Info2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>job_shadow_sponsor</t>
+          <t>job_shadow_sponsor_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Job Shadow Sponsor</t>
+          <t>Job Shadow Sponsor 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
